--- a/Översikt MALÅ.xlsx
+++ b/Översikt MALÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45559</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45952</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>45537</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>45608</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>45937</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>45937</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>46051</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>45176</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46260</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>44846</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>44472</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>44472</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>44858</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>44487</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>44858</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>44487</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>44587</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>45236</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>45022</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>45189</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>45230</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>45639</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>45158</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>45736</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>45196</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>45202</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>45195</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>45166</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>45238</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>45187</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>45201</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>45190</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>44792</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>44525</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>45184</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45638</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44928</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>45688</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>45217</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>45054</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>45166</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>45002</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>45022</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>45022</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>45244</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>45750</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>45229</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>45227</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>45225</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>45179</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>45210</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>45210</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>45252</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>45180</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>45188</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>44893</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>45643</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>45178</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>45174</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>45174</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>45645</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>45219</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>45166</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>45166</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>45625</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>45625</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>45167</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>45154</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>45197</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>45159</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>45700</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>45204</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>45204</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>45642</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>45642</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>44967</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         <v>45176</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>45174</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>45162</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>45178</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>45155</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>45158</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>45167</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>45152</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>45148</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>45890</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>45890</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>45890</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>45610</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>45166</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>45502</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         <v>45154</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>45898</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>45901</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>45897</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>45898</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>45898</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>44881</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>45154</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>45180</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>45989</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>45166</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>45170</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>45201</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>45714</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>45232</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>45111</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>45932</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>45932</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>45937</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>45939</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>45939</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>45938</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9432,7 +9432,7 @@
         <v>45937</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>45937</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>45938</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>45176</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>45149</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>45190</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>45952</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>45952</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>45719</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>45153</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>45153</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>45952</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>45952</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>45952</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>45952</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>45952</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>45267</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>45167</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>45229</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>45238</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>45960</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>45646</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>45964</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>45966</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>45201</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>45167</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>45646</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>45966</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>45966</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11614,7 +11614,7 @@
         <v>45964</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         <v>45964</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>45167</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>46154</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>44575</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11979,7 +11979,7 @@
         <v>45175</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         <v>45193</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12125,7 +12125,7 @@
         <v>45193</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v>45973</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>45384</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>45504</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>45595</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>45148</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>45719</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>44994</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>45985</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>45973</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>45987</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>45987</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>45000</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>45989</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>45989</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>45989</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>45002</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13391,7 +13391,7 @@
         <v>45989</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>45989</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>45989</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>45660</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         <v>45156</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>45166</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13844,7 +13844,7 @@
         <v>45168</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>45182</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>44911</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14063,7 +14063,7 @@
         <v>45540</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>45219</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>45902</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>45193</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14360,7 +14360,7 @@
         <v>45189</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>44524</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>45999</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>45964</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
         <v>45153</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>46001</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>46002</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>46003</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>45189</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>45694</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>45741</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15173,7 +15173,7 @@
         <v>45149</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15246,7 +15246,7 @@
         <v>45212</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15319,7 +15319,7 @@
         <v>45203</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15392,7 +15392,7 @@
         <v>45222</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15465,7 +15465,7 @@
         <v>45155</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>45154</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15611,7 +15611,7 @@
         <v>45646</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15689,7 +15689,7 @@
         <v>45516</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15762,7 +15762,7 @@
         <v>44939</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>46027</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>46027</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>44641</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>45162</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>46031</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>46031</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>46031</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>46031</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16424,7 +16424,7 @@
         <v>45161</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16502,7 +16502,7 @@
         <v>46035</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16580,7 +16580,7 @@
         <v>44893</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>45590</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>45645</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>45166</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>46042</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>45139</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>45193</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>45601</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>45154</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>45541</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>46066</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>46066</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>46070</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
         <v>45667</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>45267</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>46072</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17788,7 +17788,7 @@
         <v>45184</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>46183</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>45160</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>45625</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>46084</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>45152</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18236,7 +18236,7 @@
         <v>46185</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
         <v>45154</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>46189</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>46189</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>45201</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         <v>46189</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>46189</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>46189</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>46189</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         <v>46097</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>46097</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>46196</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>46196</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19220,7 +19220,7 @@
         <v>45159</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>45170</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>45233</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>46105</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19522,7 +19522,7 @@
         <v>46105</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19600,7 +19600,7 @@
         <v>46198</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>45642</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>45520</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>46114</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>45622</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>45642</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20053,7 +20053,7 @@
         <v>45159</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20126,7 +20126,7 @@
         <v>44491</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>45601</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
         <v>45154</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>46133</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>46133</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         <v>45520</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>46133</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>46133</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20730,7 +20730,7 @@
         <v>45222</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>45726</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45646</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>44964</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>45223</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45170</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>46246</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>46246</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21329,7 +21329,7 @@
         <v>45694</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>45369</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>45245</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>45162</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>45174</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         <v>45176</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>45170</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         <v>46248</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>46251</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>45171</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>45174</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22167,7 +22167,7 @@
         <v>46253</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22245,7 +22245,7 @@
         <v>45209</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>45700</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
         <v>46210</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>46253</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22552,7 +22552,7 @@
         <v>44802</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>45167</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22703,7 +22703,7 @@
         <v>45210</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>46253</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22854,7 +22854,7 @@
         <v>46253</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         <v>46253</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23010,7 +23010,7 @@
         <v>46253</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>45211</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         <v>45203</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>45168</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23307,7 +23307,7 @@
         <v>45516</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23380,7 +23380,7 @@
         <v>45393</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>46260</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23536,7 +23536,7 @@
         <v>45173</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23609,7 +23609,7 @@
         <v>46223</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>46223</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23765,7 +23765,7 @@
         <v>45152</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23838,7 +23838,7 @@
         <v>45153</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23911,7 +23911,7 @@
         <v>45153</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23984,7 +23984,7 @@
         <v>46185</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>46265</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>45483</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24208,7 +24208,7 @@
         <v>45636</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24281,7 +24281,7 @@
         <v>46232</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24359,7 +24359,7 @@
         <v>45152</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24432,7 +24432,7 @@
         <v>46276</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
         <v>46276</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>46276</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24651,7 +24651,7 @@
         <v>46279</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24729,7 +24729,7 @@
         <v>45454</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>44523</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24875,7 +24875,7 @@
         <v>44889</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24948,7 +24948,7 @@
         <v>45189</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25021,7 +25021,7 @@
         <v>45219</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25099,7 +25099,7 @@
         <v>45201</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>44491</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>45516</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45152</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>45799</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25464,7 +25464,7 @@
         <v>45799</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25537,7 +25537,7 @@
         <v>45798</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25610,7 +25610,7 @@
         <v>45098</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>44740</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25756,7 +25756,7 @@
         <v>45589</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>45860</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25912,7 +25912,7 @@
         <v>45861</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25990,7 +25990,7 @@
         <v>45861</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>45860</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>45861</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>45861</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>45867</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>45875</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
         <v>44607</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>

--- a/Översikt MALÅ.xlsx
+++ b/Översikt MALÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45559</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45952</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>46289</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>45537</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>46051</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>45937</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45937</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>46260</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>45176</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>45608</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>44846</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44472</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>44472</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>44858</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>44487</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>44858</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>44487</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>44587</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45209</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45219</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>45700</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>45252</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>45217</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>45393</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>45197</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>45384</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>45002</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>45267</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>44939</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>46027</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>45152</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>46027</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>45520</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>45152</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>45238</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>45174</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>45798</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>46031</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>46031</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>46031</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>45799</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>45504</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>45890</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>46035</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>45890</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>45890</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>45098</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>45154</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>45502</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>46042</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44893</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>45898</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>45898</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>45898</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>45897</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>45901</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>44928</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>45161</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>45799</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>45168</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>45516</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>46066</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>46066</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>46070</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>45139</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>44740</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>45054</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>46072</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>45932</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>45932</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>45154</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>45230</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>46084</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>45167</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>44893</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>45937</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>45174</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>45938</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>45938</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>45937</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>45937</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>45939</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>45939</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>46097</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>46097</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>45154</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>45176</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>46105</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>46105</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>45952</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>45952</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
         <v>45952</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>45952</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>45952</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>45952</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>45952</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>44994</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>45719</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>44964</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>45211</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>45694</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         <v>46114</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>45960</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8805,7 +8805,7 @@
         <v>44792</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>44491</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>45964</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>45966</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
         <v>45643</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>45966</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>45966</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         <v>45000</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>45589</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>45964</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>45964</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>45201</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>45973</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>45153</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>45153</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>45178</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>46133</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>46133</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>46133</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>46133</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>45002</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>45639</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
         <v>45184</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         <v>45985</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>45973</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>45987</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>45625</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>45989</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10889,7 +10889,7 @@
         <v>45989</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>45989</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>45989</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>45989</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
         <v>45162</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>45642</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11347,7 +11347,7 @@
         <v>45646</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>45149</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11498,7 +11498,7 @@
         <v>45203</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>45642</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>45999</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         <v>45201</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         <v>45022</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>45022</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>46001</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         <v>46002</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v>45964</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12165,7 +12165,7 @@
         <v>45714</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12243,7 +12243,7 @@
         <v>46003</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12316,7 +12316,7 @@
         <v>45989</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12389,7 +12389,7 @@
         <v>45160</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>45193</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>45212</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>45222</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>45190</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>45155</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         <v>45174</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>45166</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44802</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>45022</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>44881</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>45179</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>46154</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>45167</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         <v>45719</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>45238</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>45646</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>45148</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>45902</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>45245</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>45860</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
         <v>45860</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>45861</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         <v>45167</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14181,7 +14181,7 @@
         <v>45861</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>45158</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>45861</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>45861</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14488,7 +14488,7 @@
         <v>45156</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14561,7 +14561,7 @@
         <v>45166</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>45155</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>45152</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>45867</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>45541</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>45610</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>46183</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>45750</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>46185</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         <v>45645</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
         <v>45167</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>46189</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>46189</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>46189</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>46189</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>46189</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>45170</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>46189</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15935,7 +15935,7 @@
         <v>45154</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>45166</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16081,7 +16081,7 @@
         <v>45875</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16154,7 +16154,7 @@
         <v>46196</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>46196</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16300,7 +16300,7 @@
         <v>45590</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>45201</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>46198</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>45642</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>45162</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16665,7 +16665,7 @@
         <v>45187</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16743,7 +16743,7 @@
         <v>45189</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>45152</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>45159</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>45601</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>45174</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>45170</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>45601</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>45726</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>45645</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>45176</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>45190</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>45153</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>45153</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>45193</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>45193</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
         <v>45180</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>46251</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>45196</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>46210</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>46253</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>46253</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>46253</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18399,7 +18399,7 @@
         <v>45182</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18472,7 +18472,7 @@
         <v>45646</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>46253</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>46253</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>45204</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>46253</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18857,7 +18857,7 @@
         <v>45193</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>45625</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>45148</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>45195</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>45153</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>45201</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>45700</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>45516</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>45189</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>45232</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19592,7 +19592,7 @@
         <v>46260</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>45223</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19743,7 +19743,7 @@
         <v>45167</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>45166</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>45166</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>45162</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>45225</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>45174</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>45149</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>45202</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>45229</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>46223</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20488,7 +20488,7 @@
         <v>46223</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>45741</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>45267</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>45369</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20790,7 +20790,7 @@
         <v>46185</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>45694</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>46276</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>44575</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>46276</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>46276</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>46232</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>46279</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>45180</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>44967</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21535,7 +21535,7 @@
         <v>45167</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
         <v>45159</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>45520</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>45646</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45229</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>46265</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>45166</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>45166</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>44525</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>46289</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22285,7 +22285,7 @@
         <v>45540</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>46289</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>46289</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22514,7 +22514,7 @@
         <v>45987</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>46289</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22665,7 +22665,7 @@
         <v>46248</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>46246</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>45158</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>45154</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>46246</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>46289</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23108,7 +23108,7 @@
         <v>44641</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>46031</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23254,7 +23254,7 @@
         <v>45170</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>45736</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23405,7 +23405,7 @@
         <v>45171</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23478,7 +23478,7 @@
         <v>45184</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23551,7 +23551,7 @@
         <v>45168</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>45189</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23697,7 +23697,7 @@
         <v>45660</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>45236</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23843,7 +23843,7 @@
         <v>45210</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>45210</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>45154</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24062,7 +24062,7 @@
         <v>45188</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>45176</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24213,7 +24213,7 @@
         <v>45166</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24286,7 +24286,7 @@
         <v>45638</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24359,7 +24359,7 @@
         <v>44524</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24432,7 +24432,7 @@
         <v>45170</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>45625</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>45204</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>45244</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24729,7 +24729,7 @@
         <v>45642</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>45667</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>45595</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24958,7 +24958,7 @@
         <v>45154</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25031,7 +25031,7 @@
         <v>45233</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25104,7 +25104,7 @@
         <v>45178</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>45203</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25250,7 +25250,7 @@
         <v>45210</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>45622</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>45227</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>45173</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>45219</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>45222</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>44911</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>45111</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>45175</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>45159</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25990,7 +25990,7 @@
         <v>45636</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>45483</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>45152</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>45454</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>44889</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>44491</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>44523</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>45516</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>45189</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>45201</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>45219</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>44607</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>

--- a/Översikt MALÅ.xlsx
+++ b/Översikt MALÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45559</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45952</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>46289</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>45537</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>46051</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>45937</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45937</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>46260</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>45176</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>45608</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>44846</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44472</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>44472</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>44858</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>44487</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>44858</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>44487</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>44587</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45209</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45219</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>45700</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>45252</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>45217</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>45393</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>45197</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>45384</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>45002</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>45267</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>44939</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>46027</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>45152</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>46027</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>45520</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>45152</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>45238</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>45174</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>45798</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>46031</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>46031</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>46031</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>45799</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>45504</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>45890</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>46035</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>45890</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>45890</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>45098</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>45154</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>45502</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>46042</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44893</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>45898</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>45898</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>45898</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>45897</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>45901</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>44928</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>45161</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>45799</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>45168</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>45516</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>46066</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>46066</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>46070</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>45139</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>44740</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>45054</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>46072</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>45932</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>45932</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>45154</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>45230</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>46084</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>45167</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>44893</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>45937</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>45174</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>45938</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>45938</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>45937</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>45937</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>45939</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>45939</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>46097</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>46097</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>45154</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>45176</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>46105</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>46105</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>45952</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>45952</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
         <v>45952</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>45952</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>45952</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>45952</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>45952</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>44994</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>45719</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>44964</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>45211</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>45694</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         <v>46114</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>45960</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8805,7 +8805,7 @@
         <v>44792</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>44491</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>45964</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>45966</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
         <v>45643</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>45966</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>45966</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         <v>45000</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>45589</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>45964</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>45964</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>45201</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>45973</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>45153</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>45153</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>45178</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>46133</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>46133</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>46133</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>46133</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>45002</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>45639</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
         <v>45184</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         <v>45985</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>45973</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>45987</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>45625</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>45989</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10889,7 +10889,7 @@
         <v>45989</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>45989</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>45989</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>45989</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
         <v>45162</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>45642</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11347,7 +11347,7 @@
         <v>45646</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>45149</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11498,7 +11498,7 @@
         <v>45203</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>45642</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>45999</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         <v>45201</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         <v>45022</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>45022</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>46001</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         <v>46002</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v>45964</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12165,7 +12165,7 @@
         <v>45714</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12243,7 +12243,7 @@
         <v>46003</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12316,7 +12316,7 @@
         <v>45989</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12389,7 +12389,7 @@
         <v>45160</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>45193</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>45212</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>45222</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>45190</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>45155</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         <v>45174</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>45166</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44802</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>45022</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>44881</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>45179</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>46154</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>45167</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         <v>45719</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>45238</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>45646</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>45148</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>45902</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>45245</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>45860</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
         <v>45860</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>45861</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         <v>45167</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14181,7 +14181,7 @@
         <v>45861</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>45158</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>45861</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>45861</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14488,7 +14488,7 @@
         <v>45156</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14561,7 +14561,7 @@
         <v>45166</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>45155</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>45152</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>45867</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>45541</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>45610</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>46183</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>45750</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>46185</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         <v>45645</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
         <v>45167</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>46189</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>46189</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>46189</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>46189</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>46189</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>45170</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>46189</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15935,7 +15935,7 @@
         <v>45154</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>45166</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16081,7 +16081,7 @@
         <v>45875</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16154,7 +16154,7 @@
         <v>46196</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>46196</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16300,7 +16300,7 @@
         <v>45590</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>45201</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>46198</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>45642</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>45162</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16665,7 +16665,7 @@
         <v>45187</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16743,7 +16743,7 @@
         <v>45189</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>45152</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>45159</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>45601</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>45174</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>45170</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>45601</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>45726</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>45645</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>45176</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>45190</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>45153</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>45153</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>45193</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>45193</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
         <v>45180</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>46251</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>45196</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>46210</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>46253</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>46253</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>46253</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18399,7 +18399,7 @@
         <v>45182</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18472,7 +18472,7 @@
         <v>45646</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>46253</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>46253</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>45204</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>46253</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18857,7 +18857,7 @@
         <v>45193</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>45625</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>45148</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>45195</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>45153</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>45201</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>45700</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>45516</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>45189</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>45232</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19592,7 +19592,7 @@
         <v>46260</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>45223</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19743,7 +19743,7 @@
         <v>45167</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>45166</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>45166</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>45162</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>45225</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>45174</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>45149</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>45202</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>45229</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>46223</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20488,7 +20488,7 @@
         <v>46223</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>45741</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>45267</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>45369</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20790,7 +20790,7 @@
         <v>46185</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>45694</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>46276</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>44575</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>46276</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>46276</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>46232</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>46279</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>45180</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>44967</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21535,7 +21535,7 @@
         <v>45167</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
         <v>45159</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>45520</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>45646</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45229</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>46265</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>45166</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>45166</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>44525</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>46289</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22285,7 +22285,7 @@
         <v>45540</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>46289</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>46289</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22514,7 +22514,7 @@
         <v>45987</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>46289</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22665,7 +22665,7 @@
         <v>46248</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>46246</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>45158</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>45154</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>46246</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>46289</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23108,7 +23108,7 @@
         <v>44641</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>46031</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23254,7 +23254,7 @@
         <v>45170</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>45736</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23405,7 +23405,7 @@
         <v>45171</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23478,7 +23478,7 @@
         <v>45184</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23551,7 +23551,7 @@
         <v>45168</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>45189</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23697,7 +23697,7 @@
         <v>45660</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>45236</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23843,7 +23843,7 @@
         <v>45210</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>45210</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>45154</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24062,7 +24062,7 @@
         <v>45188</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>45176</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24213,7 +24213,7 @@
         <v>45166</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24286,7 +24286,7 @@
         <v>45638</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24359,7 +24359,7 @@
         <v>44524</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24432,7 +24432,7 @@
         <v>45170</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>45625</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>45204</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>45244</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24729,7 +24729,7 @@
         <v>45642</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>45667</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>45595</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24958,7 +24958,7 @@
         <v>45154</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25031,7 +25031,7 @@
         <v>45233</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25104,7 +25104,7 @@
         <v>45178</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>45203</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25250,7 +25250,7 @@
         <v>45210</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>45622</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>45227</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>45173</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>45219</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>45222</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>44911</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>45111</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>45175</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>45159</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25990,7 +25990,7 @@
         <v>45636</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>45483</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>45152</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>45454</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>44889</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>44491</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>44523</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>45516</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>45189</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>45201</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>45219</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>44607</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>

--- a/Översikt MALÅ.xlsx
+++ b/Översikt MALÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45559</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45952</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>46289</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>45537</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>46051</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>45937</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45937</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>45608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>46260</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>45176</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>44846</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44472</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>44472</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>44858</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>44487</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>44858</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>44487</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>44587</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45236</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45189</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>45238</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>45230</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>45022</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>45639</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>45736</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>45158</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>45202</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>45166</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>45196</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>45454</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>45201</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>46001</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>46002</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>46003</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>45195</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>44523</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>44889</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>45187</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>45212</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>45176</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>45174</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>45222</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>45190</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>45189</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>44792</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>45219</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>45201</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>44491</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>44525</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>44939</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>45890</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>45890</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>45890</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>46027</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>45502</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>46027</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>45154</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>45184</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>46031</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>46031</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>45516</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>45898</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>46031</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>45901</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>45897</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>45898</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>46035</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>45898</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>44928</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>45638</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>45217</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>46042</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>45152</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>45799</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>45799</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>45798</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>45166</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>45210</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>45210</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>45098</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>44740</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>45054</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>45002</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>45244</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>45229</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>45932</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>45932</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>45750</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>45022</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>45022</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>46066</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>46066</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>45937</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>46070</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>45939</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>45227</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>45939</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         <v>45938</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         <v>45937</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>45937</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>45938</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>46072</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>45225</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>45179</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         <v>45252</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>45952</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>45952</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>45719</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>46084</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>45180</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         <v>45952</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>45952</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>45952</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>45952</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>45952</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>45589</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>45188</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>45174</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>45174</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>44893</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>45178</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>45960</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>45643</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>45964</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>45966</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>45966</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>45966</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>45645</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>45964</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>45964</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>46097</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>46097</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>45219</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>45166</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>45166</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>45167</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>45973</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>46105</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>45625</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>45625</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>46105</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>45154</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>45985</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>46114</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>45973</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>45197</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>45159</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>45989</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>45989</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>45700</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>45989</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>45989</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>45989</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>45204</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>45204</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>45642</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>45642</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>44967</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>45162</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>45999</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>45964</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>46133</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>46133</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>45178</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>46133</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>45155</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>45158</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>45167</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>46133</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13663,7 +13663,7 @@
         <v>45148</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>45610</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
         <v>45166</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>44881</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>45154</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>45180</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>45166</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>45170</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>45201</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>45860</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>45861</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>45861</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>45860</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>45861</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>45232</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>45111</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>45861</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>45989</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>45867</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>45176</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15173,7 +15173,7 @@
         <v>45149</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15246,7 +15246,7 @@
         <v>45714</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15324,7 +15324,7 @@
         <v>45190</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15397,7 +15397,7 @@
         <v>45153</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>45153</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15543,7 +15543,7 @@
         <v>45267</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
         <v>45167</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15694,7 +15694,7 @@
         <v>45229</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>45646</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15845,7 +15845,7 @@
         <v>45238</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         <v>45875</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
         <v>46154</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45201</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>45167</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>45719</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>45646</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>45167</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>44575</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>45175</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>45193</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>45193</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>45384</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>45504</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>45902</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>45595</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>45148</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
         <v>44994</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>45000</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>45002</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>45660</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17398,7 +17398,7 @@
         <v>45156</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17471,7 +17471,7 @@
         <v>45152</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>45166</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
         <v>45168</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>45182</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17763,7 +17763,7 @@
         <v>45541</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>44911</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>45540</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>45219</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         <v>45193</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>45189</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18206,7 +18206,7 @@
         <v>44524</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18279,7 +18279,7 @@
         <v>46183</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>46185</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18435,7 +18435,7 @@
         <v>45153</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18508,7 +18508,7 @@
         <v>46189</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>46189</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>46189</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>45189</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
         <v>46189</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
         <v>46189</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         <v>46189</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19049,7 +19049,7 @@
         <v>45694</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>45741</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>45149</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>46196</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>45203</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
         <v>46196</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>45155</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>45154</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         <v>45646</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>45516</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>46198</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>44641</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>45162</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>45726</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>45161</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>44893</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20237,7 +20237,7 @@
         <v>45590</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20310,7 +20310,7 @@
         <v>45645</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>45166</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20466,7 +20466,7 @@
         <v>46210</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>45139</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
         <v>45193</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>46260</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
         <v>45601</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20851,7 +20851,7 @@
         <v>45154</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>46223</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21002,7 +21002,7 @@
         <v>46223</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         <v>45667</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21158,7 +21158,7 @@
         <v>45267</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>46185</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>45184</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>45160</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21460,7 +21460,7 @@
         <v>45625</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>46232</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>46276</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>46276</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>46276</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>46279</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>45152</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21981,7 +21981,7 @@
         <v>45154</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
         <v>45201</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
         <v>45159</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>45170</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>45233</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>45642</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>46289</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45520</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>45622</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>46265</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>46246</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>45642</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>45159</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>44491</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>46289</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23106,7 +23106,7 @@
         <v>45601</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>46289</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23262,7 +23262,7 @@
         <v>46289</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>46289</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23418,7 +23418,7 @@
         <v>45987</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23491,7 +23491,7 @@
         <v>46248</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23564,7 +23564,7 @@
         <v>45154</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>45520</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>46031</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>45222</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>46251</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>45646</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>44964</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
         <v>45223</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>46246</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24231,7 +24231,7 @@
         <v>46253</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24309,7 +24309,7 @@
         <v>46253</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>46253</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>45170</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24543,7 +24543,7 @@
         <v>45694</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24616,7 +24616,7 @@
         <v>45369</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         <v>45245</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24767,7 +24767,7 @@
         <v>46253</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>46253</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>45162</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24996,7 +24996,7 @@
         <v>45174</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>45176</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>45170</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>45987</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25298,7 +25298,7 @@
         <v>46253</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>45171</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>45174</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>45209</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>45700</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25693,7 +25693,7 @@
         <v>44802</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>45167</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>45210</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>45211</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25990,7 +25990,7 @@
         <v>45203</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>45168</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>45516</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>45393</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>45173</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>45152</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>45153</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>45153</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>45483</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>45636</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>45152</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>44607</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>

--- a/Översikt MALÅ.xlsx
+++ b/Översikt MALÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45559</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45952</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>46289</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>45537</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>46051</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>45937</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45937</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>45608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>46260</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>45176</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>44846</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44472</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>44472</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>44858</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>44487</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>44858</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>44487</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>44587</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45236</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45189</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>45238</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>45230</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>45022</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>45639</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>45736</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>45158</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>45202</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>45166</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>45196</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>45454</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>45201</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>46001</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>46002</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>46003</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>45195</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>44523</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>44889</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>45187</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>45212</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>45176</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>45174</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>45222</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>45190</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>45189</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>44792</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>45219</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>45201</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>44491</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>44525</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>44939</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>45890</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>45890</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>45890</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>46027</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>45502</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>46027</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>45154</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>45184</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>46031</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>46031</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>45516</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>45898</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>46031</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>45901</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>45897</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>45898</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>46035</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>45898</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>44928</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>45638</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>45217</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>46042</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>45152</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>45799</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>45799</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>45798</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>45166</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>45210</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>45210</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>45098</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>44740</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>45054</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>45002</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>45244</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>45229</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>45932</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>45932</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>45750</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>45022</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>45022</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>46066</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>46066</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>45937</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>46070</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>45939</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>45227</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>45939</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         <v>45938</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         <v>45937</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>45937</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>45938</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>46072</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>45225</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>45179</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         <v>45252</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>45952</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>45952</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>45719</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>46084</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>45180</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         <v>45952</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>45952</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>45952</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>45952</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>45952</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>45589</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>45188</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>45174</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>45174</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>44893</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>45178</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>45960</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>45643</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>45964</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>45966</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>45966</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>45966</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>45645</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>45964</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>45964</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>46097</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>46097</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>45219</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>45166</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>45166</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>45167</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>45973</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>46105</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>45625</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>45625</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>46105</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>45154</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>45985</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>46114</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>45973</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>45197</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>45159</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>45989</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>45989</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>45700</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>45989</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>45989</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>45989</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>45204</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>45204</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>45642</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>45642</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>44967</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>45162</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>45999</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>45964</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>46133</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>46133</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>45178</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>46133</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>45155</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>45158</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>45167</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>46133</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13663,7 +13663,7 @@
         <v>45148</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>45610</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
         <v>45166</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>44881</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>45154</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>45180</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>45166</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>45170</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>45201</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>45860</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>45861</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>45861</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>45860</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>45861</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>45232</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>45111</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>45861</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>45989</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>45867</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>45176</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15173,7 +15173,7 @@
         <v>45149</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15246,7 +15246,7 @@
         <v>45714</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15324,7 +15324,7 @@
         <v>45190</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15397,7 +15397,7 @@
         <v>45153</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>45153</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15543,7 +15543,7 @@
         <v>45267</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
         <v>45167</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15694,7 +15694,7 @@
         <v>45229</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>45646</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15845,7 +15845,7 @@
         <v>45238</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         <v>45875</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
         <v>46154</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45201</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>45167</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>45719</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>45646</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>45167</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>44575</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>45175</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>45193</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>45193</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>45384</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>45504</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>45902</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>45595</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>45148</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
         <v>44994</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>45000</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>45002</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>45660</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17398,7 +17398,7 @@
         <v>45156</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17471,7 +17471,7 @@
         <v>45152</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>45166</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
         <v>45168</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>45182</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17763,7 +17763,7 @@
         <v>45541</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>44911</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>45540</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>45219</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         <v>45193</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>45189</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18206,7 +18206,7 @@
         <v>44524</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18279,7 +18279,7 @@
         <v>46183</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>46185</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18435,7 +18435,7 @@
         <v>45153</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18508,7 +18508,7 @@
         <v>46189</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>46189</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>46189</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>45189</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
         <v>46189</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
         <v>46189</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         <v>46189</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19049,7 +19049,7 @@
         <v>45694</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>45741</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>45149</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>46196</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>45203</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
         <v>46196</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>45155</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>45154</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         <v>45646</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>45516</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>46198</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>44641</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>45162</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>45726</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>45161</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>44893</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20237,7 +20237,7 @@
         <v>45590</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20310,7 +20310,7 @@
         <v>45645</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>45166</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20466,7 +20466,7 @@
         <v>46210</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>45139</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
         <v>45193</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>46260</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
         <v>45601</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20851,7 +20851,7 @@
         <v>45154</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>46223</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21002,7 +21002,7 @@
         <v>46223</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         <v>45667</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21158,7 +21158,7 @@
         <v>45267</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>46185</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>45184</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>45160</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21460,7 +21460,7 @@
         <v>45625</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>46232</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>46276</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>46276</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>46276</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>46279</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>45152</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21981,7 +21981,7 @@
         <v>45154</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
         <v>45201</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
         <v>45159</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>45170</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>45233</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>45642</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>46289</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45520</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>45622</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>46265</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>46246</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>45642</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>45159</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>44491</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>46289</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23106,7 +23106,7 @@
         <v>45601</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>46289</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23262,7 +23262,7 @@
         <v>46289</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>46289</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23418,7 +23418,7 @@
         <v>45987</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23491,7 +23491,7 @@
         <v>46248</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23564,7 +23564,7 @@
         <v>45154</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>45520</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>46031</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>45222</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>46251</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>45646</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>44964</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
         <v>45223</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>46246</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24231,7 +24231,7 @@
         <v>46253</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24309,7 +24309,7 @@
         <v>46253</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>46253</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>45170</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24543,7 +24543,7 @@
         <v>45694</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24616,7 +24616,7 @@
         <v>45369</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         <v>45245</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24767,7 +24767,7 @@
         <v>46253</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>46253</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>45162</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24996,7 +24996,7 @@
         <v>45174</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>45176</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>45170</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>45987</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25298,7 +25298,7 @@
         <v>46253</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>45171</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>45174</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>45209</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>45700</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25693,7 +25693,7 @@
         <v>44802</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>45167</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>45210</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>45211</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25990,7 +25990,7 @@
         <v>45203</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>45168</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>45516</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>45393</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>45173</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>45152</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>45153</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>45153</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>45483</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>45636</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>45152</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>44607</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>

--- a/Översikt MALÅ.xlsx
+++ b/Översikt MALÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45559</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45952</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>46289</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>45537</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>45608</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>45937</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45937</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>45176</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>46051</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>46260</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>44846</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44858</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>44487</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>44858</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>44487</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>44587</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45154</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>45188</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45176</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>45179</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>45217</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>45166</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>45638</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>45252</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>45167</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>44524</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>45209</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>45219</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>45170</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>45625</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>45204</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>45244</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>45393</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45642</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>45667</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>45384</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>45595</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>45197</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>45646</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>45002</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>45148</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>45154</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>45245</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>45233</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>45267</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>45700</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>45178</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>45174</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>45203</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>45176</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>45210</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>45622</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>45227</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>45152</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>45173</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>45219</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>45167</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>45520</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>45158</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>45222</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>45890</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>45156</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>45238</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>45890</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>45166</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>45174</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>45890</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>45154</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>45502</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>45898</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>45898</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>44911</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>45898</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>45504</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>45111</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>45897</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>45901</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
         <v>45175</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>45155</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>45152</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>44893</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>45610</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         <v>45159</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>44928</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>45161</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>45636</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>45483</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>45750</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>45645</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>45167</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>45152</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>45168</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>45454</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>45170</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>45154</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>45516</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>45166</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>45139</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>44889</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>45054</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>44491</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>44523</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>45516</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         <v>45590</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>45189</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>45201</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>45219</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>45201</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>45152</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>45154</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>45932</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>45230</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         <v>45642</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>45932</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>45162</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>45167</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>45187</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>45189</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>45798</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>45152</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>44893</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>45799</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>45174</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>45098</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>45159</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>45601</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>45170</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>45799</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>45601</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>45645</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>45937</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>45190</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>45154</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>44740</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         <v>45153</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>45153</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         <v>45938</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>45193</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>45193</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>45176</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>45938</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>45180</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>45937</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         <v>45937</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>45196</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>45939</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>45939</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>45182</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>45646</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         <v>44994</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>45589</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>45204</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>44964</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>45193</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         <v>45211</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>45625</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>45148</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>45694</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>44792</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>45195</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>44491</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>45153</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>45201</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>45643</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>45700</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13391,7 +13391,7 @@
         <v>45952</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>45952</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>45952</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>45516</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13688,7 +13688,7 @@
         <v>45189</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>45952</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>45000</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13912,7 +13912,7 @@
         <v>45232</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>45952</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14063,7 +14063,7 @@
         <v>45952</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>45952</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>45719</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14282,7 +14282,7 @@
         <v>45201</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
         <v>45960</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>45223</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>45167</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>45166</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
         <v>45166</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14730,7 +14730,7 @@
         <v>45153</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>45153</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>45162</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>45178</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>45964</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>45225</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>45966</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15246,7 +15246,7 @@
         <v>45966</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15319,7 +15319,7 @@
         <v>45174</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15392,7 +15392,7 @@
         <v>45966</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>45002</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
         <v>45639</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
         <v>45149</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15694,7 +15694,7 @@
         <v>45184</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15772,7 +15772,7 @@
         <v>45202</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15845,7 +15845,7 @@
         <v>45229</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>45625</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>45964</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>45964</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>45973</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>45162</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>45642</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>45646</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
         <v>45741</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         <v>45149</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16580,7 +16580,7 @@
         <v>45203</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>45267</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>45642</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>45860</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>45860</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         <v>45201</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>45861</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>45861</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>45369</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>45861</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>45861</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
         <v>45022</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>45022</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>45160</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>45193</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>45694</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         <v>45875</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17871,7 +17871,7 @@
         <v>45190</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17944,7 +17944,7 @@
         <v>45155</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>44575</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>46097</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>45180</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18236,7 +18236,7 @@
         <v>45985</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>44967</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>46105</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         <v>45167</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18533,7 +18533,7 @@
         <v>45159</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         <v>46105</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18684,7 +18684,7 @@
         <v>45174</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>45166</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         <v>45520</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>45973</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>45646</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19064,7 +19064,7 @@
         <v>45229</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>45989</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19215,7 +19215,7 @@
         <v>45989</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>45989</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>45989</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>45989</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>44802</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19600,7 +19600,7 @@
         <v>45022</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>44881</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>46114</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>45999</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>46001</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>46002</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>46003</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>46133</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>46133</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         <v>46133</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>46133</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>45166</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20496,7 +20496,7 @@
         <v>45166</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
         <v>44525</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>45540</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>45158</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>45154</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>45212</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>45222</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>44641</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         <v>44939</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21158,7 +21158,7 @@
         <v>46027</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>46027</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         <v>45714</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>45989</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>46031</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         <v>46031</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>46031</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>45170</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21752,7 +21752,7 @@
         <v>45736</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21825,7 +21825,7 @@
         <v>45171</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>46035</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>45184</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>46042</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
         <v>45168</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>45189</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>45660</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22346,7 +22346,7 @@
         <v>45236</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22419,7 +22419,7 @@
         <v>45210</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>45210</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22565,7 +22565,7 @@
         <v>46066</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>46066</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>46070</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>46072</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>46154</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>45719</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23008,7 +23008,7 @@
         <v>45238</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>46084</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>46097</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23232,7 +23232,7 @@
         <v>45902</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>45541</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>46183</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>46185</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>46189</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         <v>46189</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23690,7 +23690,7 @@
         <v>46189</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         <v>46189</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23846,7 +23846,7 @@
         <v>46189</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>46189</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>46196</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>46196</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24148,7 +24148,7 @@
         <v>46198</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>45726</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>46210</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>46223</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>46223</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>46185</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>46276</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>46276</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24752,7 +24752,7 @@
         <v>46276</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24825,7 +24825,7 @@
         <v>46232</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>46279</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>46265</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         <v>46289</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25137,7 +25137,7 @@
         <v>46289</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25215,7 +25215,7 @@
         <v>46289</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>45987</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>46289</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25444,7 +25444,7 @@
         <v>46248</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25517,7 +25517,7 @@
         <v>46246</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25590,7 +25590,7 @@
         <v>46289</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>46031</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25741,7 +25741,7 @@
         <v>46251</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         <v>46253</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>46253</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25970,7 +25970,7 @@
         <v>46253</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26048,7 +26048,7 @@
         <v>46253</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>46253</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>45987</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>46246</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>46253</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>46260</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>45867</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>44607</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>

--- a/Översikt MALÅ.xlsx
+++ b/Översikt MALÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45559</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45952</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>46289</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>45537</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>45608</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>45937</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45937</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>45176</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>46051</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>46260</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>44846</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44858</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>44487</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>44858</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>44487</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>44587</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45154</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>45188</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45176</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>45179</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>45217</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>45166</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>45638</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>45252</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>45167</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>44524</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>45209</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>45219</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>45170</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>45625</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>45204</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>45244</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>45393</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45642</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>45667</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>45384</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>45595</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>45197</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>45646</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>45002</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>45148</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>45154</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>45245</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>45233</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>45267</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>45700</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>45178</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>45174</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>45203</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>45176</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>45210</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>45622</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>45227</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>45152</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>45173</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>45219</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>45167</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>45520</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>45158</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>45222</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>45890</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>45156</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>45238</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>45890</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>45166</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>45174</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>45890</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>45154</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>45502</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>45898</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>45898</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>44911</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>45898</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>45504</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>45111</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>45897</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>45901</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
         <v>45175</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>45155</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>45152</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>44893</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>45610</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         <v>45159</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>44928</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>45161</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>45636</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>45483</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>45750</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>45645</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>45167</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>45152</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>45168</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>45454</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>45170</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>45154</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>45516</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>45166</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>45139</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>44889</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>45054</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>44491</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>44523</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>45516</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         <v>45590</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>45189</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>45201</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>45219</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>45201</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>45152</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>45154</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>45932</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>45230</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         <v>45642</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>45932</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>45162</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>45167</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>45187</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>45189</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>45798</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>45152</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>44893</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>45799</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>45174</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>45098</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>45159</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>45601</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>45170</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>45799</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>45601</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>45645</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>45937</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>45190</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>45154</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>44740</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         <v>45153</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>45153</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         <v>45938</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>45193</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>45193</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>45176</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>45938</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>45180</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>45937</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         <v>45937</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>45196</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>45939</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>45939</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>45182</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>45646</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         <v>44994</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>45589</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>45204</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>44964</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>45193</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         <v>45211</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>45625</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>45148</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>45694</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>44792</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>45195</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>44491</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>45153</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>45201</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>45643</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>45700</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13391,7 +13391,7 @@
         <v>45952</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>45952</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>45952</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>45516</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13688,7 +13688,7 @@
         <v>45189</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>45952</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>45000</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13912,7 +13912,7 @@
         <v>45232</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>45952</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14063,7 +14063,7 @@
         <v>45952</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>45952</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>45719</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14282,7 +14282,7 @@
         <v>45201</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
         <v>45960</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>45223</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>45167</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>45166</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
         <v>45166</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14730,7 +14730,7 @@
         <v>45153</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>45153</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>45162</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>45178</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>45964</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>45225</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>45966</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15246,7 +15246,7 @@
         <v>45966</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15319,7 +15319,7 @@
         <v>45174</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15392,7 +15392,7 @@
         <v>45966</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>45002</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
         <v>45639</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
         <v>45149</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15694,7 +15694,7 @@
         <v>45184</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15772,7 +15772,7 @@
         <v>45202</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15845,7 +15845,7 @@
         <v>45229</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>45625</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>45964</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>45964</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>45973</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>45162</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>45642</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>45646</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
         <v>45741</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         <v>45149</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16580,7 +16580,7 @@
         <v>45203</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>45267</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>45642</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>45860</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>45860</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         <v>45201</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>45861</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>45861</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>45369</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>45861</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>45861</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
         <v>45022</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>45022</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>45160</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>45193</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>45694</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         <v>45875</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17871,7 +17871,7 @@
         <v>45190</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17944,7 +17944,7 @@
         <v>45155</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>44575</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>46097</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>45180</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18236,7 +18236,7 @@
         <v>45985</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>44967</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>46105</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         <v>45167</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18533,7 +18533,7 @@
         <v>45159</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         <v>46105</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18684,7 +18684,7 @@
         <v>45174</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>45166</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         <v>45520</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>45973</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>45646</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19064,7 +19064,7 @@
         <v>45229</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>45989</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19215,7 +19215,7 @@
         <v>45989</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>45989</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>45989</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>45989</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>44802</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19600,7 +19600,7 @@
         <v>45022</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>44881</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>46114</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>45999</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>46001</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>46002</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>46003</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>46133</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>46133</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         <v>46133</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>46133</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>45166</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20496,7 +20496,7 @@
         <v>45166</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
         <v>44525</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>45540</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>45158</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>45154</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>45212</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>45222</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>44641</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         <v>44939</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21158,7 +21158,7 @@
         <v>46027</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>46027</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         <v>45714</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>45989</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>46031</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         <v>46031</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>46031</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>45170</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21752,7 +21752,7 @@
         <v>45736</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21825,7 +21825,7 @@
         <v>45171</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>46035</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>45184</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>46042</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
         <v>45168</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>45189</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>45660</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22346,7 +22346,7 @@
         <v>45236</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22419,7 +22419,7 @@
         <v>45210</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>45210</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22565,7 +22565,7 @@
         <v>46066</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>46066</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>46070</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>46072</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>46154</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>45719</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23008,7 +23008,7 @@
         <v>45238</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>46084</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>46097</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23232,7 +23232,7 @@
         <v>45902</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>45541</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>46183</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>46185</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>46189</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         <v>46189</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23690,7 +23690,7 @@
         <v>46189</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         <v>46189</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23846,7 +23846,7 @@
         <v>46189</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>46189</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>46196</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>46196</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24148,7 +24148,7 @@
         <v>46198</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>45726</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>46210</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>46223</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>46223</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>46185</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>46276</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>46276</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24752,7 +24752,7 @@
         <v>46276</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24825,7 +24825,7 @@
         <v>46232</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>46279</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>46265</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         <v>46289</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25137,7 +25137,7 @@
         <v>46289</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25215,7 +25215,7 @@
         <v>46289</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>45987</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>46289</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25444,7 +25444,7 @@
         <v>46248</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25517,7 +25517,7 @@
         <v>46246</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25590,7 +25590,7 @@
         <v>46289</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>46031</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25741,7 +25741,7 @@
         <v>46251</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         <v>46253</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>46253</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25970,7 +25970,7 @@
         <v>46253</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26048,7 +26048,7 @@
         <v>46253</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>46253</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>45987</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>46246</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>46253</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>46260</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>45867</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>44607</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>

--- a/Översikt MALÅ.xlsx
+++ b/Översikt MALÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45559</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46309</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45552</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>45952</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>46289</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>45537</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>45608</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>45937</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>45937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>46051</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>45176</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>46260</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>46309</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>44846</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>44858</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>44487</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44858</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>44487</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>44587</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>45236</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>45238</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>45022</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45189</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>45230</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>45639</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>45158</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>45736</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>45202</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>45196</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45166</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>45201</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>45187</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>45195</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45190</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>44792</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>44525</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45184</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>45638</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>44928</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>45217</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>45166</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>45054</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>45210</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>45210</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>45022</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>45022</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>45750</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>45227</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>45225</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>45179</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>45252</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>45180</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>45002</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>45188</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>44893</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>45178</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>45174</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>45174</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>45643</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>45645</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>45244</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5588,7 +5588,7 @@
         <v>45219</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>45166</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>45166</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>45167</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>45625</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>45625</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>45154</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>45229</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>45197</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>45159</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>45700</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>45204</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>45204</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>45176</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>45174</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>45642</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>45642</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>44967</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>45152</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>45890</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>45162</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>45890</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>45890</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
         <v>45502</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         <v>45154</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>45178</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         <v>45155</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>45158</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         <v>45167</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>45898</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         <v>45901</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>45148</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>45897</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>45898</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>45898</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>45989</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>45610</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>45166</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>45714</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>44881</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>45154</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>45180</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>45166</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>45170</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>45201</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>45932</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>45932</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>45937</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>45939</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>45939</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>45938</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>45937</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
         <v>45937</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>45238</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>45938</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>45232</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>45111</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>46154</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         <v>45952</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>45952</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>45719</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>45952</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>45952</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>45952</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>45952</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>45952</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>45719</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10604,7 +10604,7 @@
         <v>45176</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>45960</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>45964</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>45966</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>45149</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>45966</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>45190</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>45966</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
         <v>45964</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>45964</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>45973</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>45153</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>45153</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>45267</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>45902</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>45167</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>45229</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
         <v>45646</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11943,7 +11943,7 @@
         <v>45985</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>45201</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
         <v>45973</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>45167</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>45646</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>45167</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>45989</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>45989</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
         <v>45989</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>45989</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>45989</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>44575</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>45175</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>45193</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>45193</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13068,7 +13068,7 @@
         <v>45384</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>45504</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>45999</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>45595</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>46001</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>46002</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>46003</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>45148</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>44994</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>45000</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>45002</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>45212</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>45660</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>45156</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>45222</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>45166</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>45168</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>45182</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>44939</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>44911</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>45540</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>45219</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>46027</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>46027</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>45193</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>45189</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>46031</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>44524</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>46031</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>46031</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
         <v>46035</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>45153</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>45541</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>46042</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>45189</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
         <v>45694</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>45741</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>45149</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         <v>45203</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>45155</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>45154</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>46183</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>45646</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         <v>45516</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>46066</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>46066</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>46070</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>46072</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>44641</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>46185</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         <v>45162</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         <v>45161</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         <v>44893</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>46084</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>45590</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>46189</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
         <v>46189</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>45645</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>45166</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>46189</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>46189</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>46189</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>46189</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>46097</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>46097</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>46196</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17991,7 +17991,7 @@
         <v>45139</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>45193</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>46196</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>45601</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18293,7 +18293,7 @@
         <v>46105</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>46105</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>45154</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>46114</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>46198</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18673,7 +18673,7 @@
         <v>45667</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>45267</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>45184</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>46133</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>46133</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19053,7 +19053,7 @@
         <v>45160</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19131,7 +19131,7 @@
         <v>46133</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>45625</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19282,7 +19282,7 @@
         <v>46133</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>45726</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>45152</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19506,7 +19506,7 @@
         <v>45154</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
         <v>45201</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19652,7 +19652,7 @@
         <v>46210</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19730,7 +19730,7 @@
         <v>45159</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19803,7 +19803,7 @@
         <v>45170</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         <v>45233</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
         <v>45642</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>45520</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>45622</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>46223</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>46223</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         <v>45642</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         <v>45159</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>46185</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20558,7 +20558,7 @@
         <v>44491</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20631,7 +20631,7 @@
         <v>45601</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20709,7 +20709,7 @@
         <v>46232</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20787,7 +20787,7 @@
         <v>45154</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         <v>45520</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         <v>46276</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21011,7 +21011,7 @@
         <v>46276</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         <v>46276</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>45222</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21230,7 +21230,7 @@
         <v>46279</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45646</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21386,7 +21386,7 @@
         <v>44964</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>45223</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>45170</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>45694</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>45369</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>45245</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>45162</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>45174</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>45176</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         <v>45170</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>45171</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22209,7 +22209,7 @@
         <v>45174</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>45209</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>45700</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22453,7 +22453,7 @@
         <v>44802</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>45167</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>45210</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>45211</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>46289</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>46265</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>45203</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22979,7 +22979,7 @@
         <v>46246</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>45168</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>46289</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23203,7 +23203,7 @@
         <v>45516</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23276,7 +23276,7 @@
         <v>46289</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>46289</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23432,7 +23432,7 @@
         <v>46289</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23510,7 +23510,7 @@
         <v>45393</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>45987</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>46248</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23734,7 +23734,7 @@
         <v>46031</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23807,7 +23807,7 @@
         <v>45173</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23880,7 +23880,7 @@
         <v>46251</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>46246</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24026,7 +24026,7 @@
         <v>46253</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>46253</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24182,7 +24182,7 @@
         <v>46253</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24260,7 +24260,7 @@
         <v>46253</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24338,7 +24338,7 @@
         <v>46253</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24416,7 +24416,7 @@
         <v>45987</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24489,7 +24489,7 @@
         <v>46253</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>45152</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>45153</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>45153</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>45483</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>45636</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>45152</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25005,7 +25005,7 @@
         <v>46260</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25083,7 +25083,7 @@
         <v>45454</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
         <v>44523</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>44889</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>45189</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>45219</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>45201</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25526,7 +25526,7 @@
         <v>44491</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>45516</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>45152</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25745,7 +25745,7 @@
         <v>45867</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>45799</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>45799</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
         <v>45798</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         <v>46309</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26115,7 +26115,7 @@
         <v>45098</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>44740</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>46310</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26339,7 +26339,7 @@
         <v>46310</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>45589</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>45860</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26573,7 +26573,7 @@
         <v>45861</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>45861</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>45860</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>45861</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26885,7 +26885,7 @@
         <v>45861</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         <v>45875</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27036,7 +27036,7 @@
         <v>44607</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>

--- a/Översikt MALÅ.xlsx
+++ b/Översikt MALÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45559</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46309</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45552</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>45952</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>46289</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>45537</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>45608</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>45937</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>45937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>46051</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>45176</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>46260</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>46309</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>44846</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>44858</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>44487</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44858</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>44487</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>44587</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>45236</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>45238</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>45022</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45189</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>45230</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>45639</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>45158</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>45736</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>45202</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>45196</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45166</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>45201</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>45187</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>45195</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45190</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>44792</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>44525</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45184</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>45638</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>44928</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>45217</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>45166</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>45054</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>45210</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>45210</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>45022</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>45022</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>45750</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>45227</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>45225</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>45179</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>45252</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>45180</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>45002</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>45188</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>44893</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>45178</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>45174</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>45174</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>45643</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>45645</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>45244</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5588,7 +5588,7 @@
         <v>45219</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>45166</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>45166</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>45167</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>45625</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>45625</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>45154</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>45229</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>45197</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>45159</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>45700</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>45204</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>45204</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>45176</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>45174</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>45642</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>45642</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>44967</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>45152</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>45890</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>45162</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>45890</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>45890</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
         <v>45502</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         <v>45154</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>45178</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         <v>45155</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>45158</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         <v>45167</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>45898</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         <v>45901</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>45148</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>45897</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>45898</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>45898</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>45989</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>45610</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>45166</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>45714</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>44881</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>45154</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>45180</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>45166</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>45170</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>45201</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>45932</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>45932</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>45937</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>45939</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>45939</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>45938</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>45937</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
         <v>45937</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>45238</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>45938</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>45232</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>45111</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>46154</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         <v>45952</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>45952</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>45719</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>45952</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>45952</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>45952</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>45952</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>45952</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>45719</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10604,7 +10604,7 @@
         <v>45176</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>45960</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>45964</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>45966</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>45149</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>45966</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>45190</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>45966</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
         <v>45964</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>45964</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>45973</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>45153</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>45153</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>45267</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>45902</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>45167</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>45229</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
         <v>45646</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11943,7 +11943,7 @@
         <v>45985</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>45201</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
         <v>45973</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>45167</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>45646</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>45167</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>45989</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>45989</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
         <v>45989</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>45989</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>45989</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>44575</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>45175</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>45193</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>45193</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13068,7 +13068,7 @@
         <v>45384</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>45504</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>45999</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>45595</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>46001</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>46002</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>46003</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>45148</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>44994</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>45000</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>45002</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>45212</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>45660</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>45156</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>45222</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>45166</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>45168</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>45182</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>44939</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>44911</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>45540</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>45219</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>46027</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>46027</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>45193</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>45189</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>46031</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>44524</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>46031</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>46031</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
         <v>46035</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>45153</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>45541</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>46042</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>45189</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
         <v>45694</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>45741</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>45149</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         <v>45203</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>45155</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>45154</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>46183</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>45646</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         <v>45516</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>46066</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>46066</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>46070</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>46072</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>44641</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>46185</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         <v>45162</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         <v>45161</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         <v>44893</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>46084</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>45590</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>46189</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
         <v>46189</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>45645</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>45166</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>46189</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>46189</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>46189</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>46189</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>46097</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>46097</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>46196</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17991,7 +17991,7 @@
         <v>45139</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>45193</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>46196</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>45601</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18293,7 +18293,7 @@
         <v>46105</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>46105</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>45154</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>46114</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>46198</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18673,7 +18673,7 @@
         <v>45667</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>45267</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>45184</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>46133</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>46133</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19053,7 +19053,7 @@
         <v>45160</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19131,7 +19131,7 @@
         <v>46133</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>45625</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19282,7 +19282,7 @@
         <v>46133</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>45726</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>45152</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19506,7 +19506,7 @@
         <v>45154</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
         <v>45201</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19652,7 +19652,7 @@
         <v>46210</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19730,7 +19730,7 @@
         <v>45159</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19803,7 +19803,7 @@
         <v>45170</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         <v>45233</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
         <v>45642</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>45520</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>45622</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>46223</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>46223</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         <v>45642</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         <v>45159</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>46185</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20558,7 +20558,7 @@
         <v>44491</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20631,7 +20631,7 @@
         <v>45601</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20709,7 +20709,7 @@
         <v>46232</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20787,7 +20787,7 @@
         <v>45154</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         <v>45520</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         <v>46276</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21011,7 +21011,7 @@
         <v>46276</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         <v>46276</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>45222</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21230,7 +21230,7 @@
         <v>46279</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45646</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21386,7 +21386,7 @@
         <v>44964</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>45223</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>45170</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>45694</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>45369</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>45245</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>45162</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>45174</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>45176</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         <v>45170</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>45171</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22209,7 +22209,7 @@
         <v>45174</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>45209</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>45700</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22453,7 +22453,7 @@
         <v>44802</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>45167</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>45210</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>45211</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>46289</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>46265</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>45203</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22979,7 +22979,7 @@
         <v>46246</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>45168</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>46289</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23203,7 +23203,7 @@
         <v>45516</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23276,7 +23276,7 @@
         <v>46289</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>46289</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23432,7 +23432,7 @@
         <v>46289</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23510,7 +23510,7 @@
         <v>45393</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>45987</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>46248</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23734,7 +23734,7 @@
         <v>46031</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23807,7 +23807,7 @@
         <v>45173</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23880,7 +23880,7 @@
         <v>46251</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>46246</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24026,7 +24026,7 @@
         <v>46253</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>46253</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24182,7 +24182,7 @@
         <v>46253</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24260,7 +24260,7 @@
         <v>46253</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24338,7 +24338,7 @@
         <v>46253</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24416,7 +24416,7 @@
         <v>45987</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24489,7 +24489,7 @@
         <v>46253</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>45152</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>45153</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>45153</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>45483</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>45636</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>45152</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25005,7 +25005,7 @@
         <v>46260</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25083,7 +25083,7 @@
         <v>45454</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
         <v>44523</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>44889</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>45189</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>45219</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>45201</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25526,7 +25526,7 @@
         <v>44491</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>45516</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>45152</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25745,7 +25745,7 @@
         <v>45867</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>45799</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>45799</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
         <v>45798</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         <v>46309</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26115,7 +26115,7 @@
         <v>45098</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>44740</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>46310</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26339,7 +26339,7 @@
         <v>46310</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>45589</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>45860</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26573,7 +26573,7 @@
         <v>45861</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>45861</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>45860</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>45861</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26885,7 +26885,7 @@
         <v>45861</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         <v>45875</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27036,7 +27036,7 @@
         <v>44607</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>

--- a/Översikt MALÅ.xlsx
+++ b/Översikt MALÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45559</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>46309</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>45952</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>46289</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>45537</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>45937</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>45937</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>45608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>46051</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>46260</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>46309</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>46314</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>45176</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>44846</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>44858</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>44858</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>44587</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>45176</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>45166</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>45166</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>44525</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45540</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>45209</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>45890</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>45219</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>45890</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>45890</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>45154</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>45502</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>45158</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>45154</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>45898</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>45700</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>45898</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>45898</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>45152</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44641</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>45897</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>45901</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>45902</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>45217</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>45170</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>45736</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>45171</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>45184</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>45168</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>45189</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>45660</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>45932</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>45236</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>45932</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>45210</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>45210</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>45252</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>45937</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>45938</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>45938</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>45937</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>45937</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>45939</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>45154</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>45939</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>45188</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>45176</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>45166</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>45638</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>45541</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>45393</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>45384</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>45197</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>45002</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>44524</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>45267</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>45952</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         <v>45952</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>45952</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>45170</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>45952</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>45952</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>46183</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>45952</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>45952</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>45719</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>45625</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>45204</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>46185</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>45244</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
         <v>45960</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>45642</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>45667</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7920,7 +7920,7 @@
         <v>46189</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>46189</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>46189</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>46189</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>45595</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>45964</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>46189</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>45966</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>45154</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>46189</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>45966</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>45233</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>45966</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>45178</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>46196</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         <v>46196</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>45203</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>45964</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>45964</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>45210</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>45973</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>45622</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>45227</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>45173</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>46198</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>45219</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>45222</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>45726</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>45985</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>45973</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>44911</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>46210</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>45989</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10399,7 +10399,7 @@
         <v>45111</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>45989</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>45989</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>45989</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>45989</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>45175</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10857,7 +10857,7 @@
         <v>45999</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
         <v>45159</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>46223</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>46223</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         <v>46001</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>46002</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>45636</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>46003</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>45483</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         <v>46185</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>46232</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>45212</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>46279</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>45222</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
         <v>45152</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>45454</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>44939</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>46027</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>46027</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>44889</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>44523</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>45516</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>46031</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>46031</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
         <v>46031</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>45189</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>45201</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>45219</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>46035</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
         <v>45152</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>46042</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>45798</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>46265</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>45799</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>45098</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>45799</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>46289</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>46289</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>46289</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         <v>45987</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>46289</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>46248</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>46246</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>45520</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>44740</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>46289</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>46031</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>45589</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>46066</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14519,7 +14519,7 @@
         <v>46066</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>46070</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>46072</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>46251</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>46253</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>46253</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>46253</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>46253</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>46253</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>46084</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>45238</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>45987</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>46097</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15503,7 +15503,7 @@
         <v>45174</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         <v>46097</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>46246</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>46253</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15800,7 +15800,7 @@
         <v>46105</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>46105</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>45504</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         <v>45860</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>45860</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>45861</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>45861</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>45861</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>45861</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>46114</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         <v>46260</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>45875</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>45867</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16799,7 +16799,7 @@
         <v>44893</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         <v>46133</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>45174</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>46133</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>46133</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>46133</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>44928</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>45161</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17398,7 +17398,7 @@
         <v>46310</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>46310</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17554,7 +17554,7 @@
         <v>46309</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>45168</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>46314</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>45516</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>45714</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>45989</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>45139</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         <v>45054</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>45154</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>45230</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>45167</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>46276</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>46276</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>46276</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>44893</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>46317</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18747,7 +18747,7 @@
         <v>46317</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>46317</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
         <v>45174</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>45154</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>45176</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>46154</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19210,7 +19210,7 @@
         <v>45719</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>45238</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44994</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19434,7 +19434,7 @@
         <v>44964</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19507,7 +19507,7 @@
         <v>45211</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19580,7 +19580,7 @@
         <v>45694</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>44792</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19726,7 +19726,7 @@
         <v>45643</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>45000</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
         <v>45201</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>45153</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>45153</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         <v>45178</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>45002</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>45639</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>45184</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>45625</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20466,7 +20466,7 @@
         <v>45162</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>45642</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>45646</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>45149</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>45203</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>45642</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>45201</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20987,7 +20987,7 @@
         <v>45022</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
         <v>45022</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>45160</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21211,7 +21211,7 @@
         <v>45193</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21284,7 +21284,7 @@
         <v>45190</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>45155</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>45174</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>45166</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21581,7 +21581,7 @@
         <v>44802</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>45022</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>44881</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21800,7 +21800,7 @@
         <v>45179</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21873,7 +21873,7 @@
         <v>45167</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21946,7 +21946,7 @@
         <v>45646</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>45148</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>45245</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22175,7 +22175,7 @@
         <v>45167</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         <v>45158</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>45156</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>45166</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22472,7 +22472,7 @@
         <v>45155</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22545,7 +22545,7 @@
         <v>45152</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22618,7 +22618,7 @@
         <v>45610</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>45750</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22764,7 +22764,7 @@
         <v>45645</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22842,7 +22842,7 @@
         <v>45167</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22920,7 +22920,7 @@
         <v>45170</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>45154</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>45166</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>45590</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23217,7 +23217,7 @@
         <v>45201</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23290,7 +23290,7 @@
         <v>45642</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>45162</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23436,7 +23436,7 @@
         <v>45187</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23514,7 +23514,7 @@
         <v>45189</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         <v>45152</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23660,7 +23660,7 @@
         <v>45159</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23733,7 +23733,7 @@
         <v>45601</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23811,7 +23811,7 @@
         <v>45170</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>45601</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>45645</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>45190</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>45153</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
         <v>45153</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>45193</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>45193</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>45180</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>45196</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24556,7 +24556,7 @@
         <v>45182</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>45646</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24707,7 +24707,7 @@
         <v>45204</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24780,7 +24780,7 @@
         <v>45193</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>45625</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24926,7 +24926,7 @@
         <v>45148</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>45195</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25072,7 +25072,7 @@
         <v>45153</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>45201</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25218,7 +25218,7 @@
         <v>45700</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>45516</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>45189</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>45232</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>45223</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>45167</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>45166</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>45166</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>45162</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>45225</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>45174</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>45149</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>45202</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>45229</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>45741</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>45267</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>45369</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>45694</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26557,7 +26557,7 @@
         <v>44575</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26630,7 +26630,7 @@
         <v>45180</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26703,7 +26703,7 @@
         <v>44967</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26776,7 +26776,7 @@
         <v>45167</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>45159</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>45520</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>45646</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>45229</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>44607</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>

--- a/Översikt MALÅ.xlsx
+++ b/Översikt MALÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45559</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45552</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>46309</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>45952</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>46289</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>45537</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>45937</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>45937</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>45608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>46051</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>46260</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>46309</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>46314</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>45176</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>44846</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>44858</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>44858</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>44587</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>45176</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>45166</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>45166</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>44525</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45540</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>45209</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>45890</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>45219</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>45890</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>45890</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>45154</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>45502</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>45158</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>45154</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>45898</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>45700</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>45898</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>45898</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>45152</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44641</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>45897</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>45901</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>45902</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>45217</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>45170</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>45736</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>45171</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>45184</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>45168</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>45189</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>45660</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>45932</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>45236</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>45932</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>45210</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>45210</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>45252</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>45937</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>45938</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>45938</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>45937</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>45937</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>45939</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>45154</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>45939</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>45188</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>45176</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>45166</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>45638</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>45541</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>45393</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>45384</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>45197</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>45002</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>44524</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>45267</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>45952</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         <v>45952</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>45952</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>45170</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>45952</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>45952</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>46183</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>45952</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>45952</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>45719</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>45625</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>45204</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>46185</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>45244</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
         <v>45960</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>45642</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>45667</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7920,7 +7920,7 @@
         <v>46189</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>46189</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>46189</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>46189</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>45595</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>45964</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>46189</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>45966</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>45154</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>46189</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>45966</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>45233</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>45966</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>45178</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>46196</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         <v>46196</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>45203</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>45964</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>45964</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>45210</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>45973</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>45622</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>45227</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>45173</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>46198</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>45219</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>45222</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>45726</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>45985</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>45973</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>44911</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>46210</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>45989</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10399,7 +10399,7 @@
         <v>45111</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>45989</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>45989</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>45989</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>45989</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>45175</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10857,7 +10857,7 @@
         <v>45999</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
         <v>45159</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>46223</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>46223</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         <v>46001</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>46002</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>45636</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>46003</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>45483</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         <v>46185</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>46232</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>45212</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>46279</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>45222</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
         <v>45152</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>45454</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>44939</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>46027</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>46027</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>44889</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>44523</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>45516</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>46031</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>46031</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
         <v>46031</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>45189</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>45201</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>45219</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>46035</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
         <v>45152</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>46042</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>45798</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>46265</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>45799</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>45098</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>45799</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>46289</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>46289</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>46289</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         <v>45987</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>46289</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>46248</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>46246</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>45520</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>44740</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>46289</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>46031</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>45589</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>46066</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14519,7 +14519,7 @@
         <v>46066</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>46070</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>46072</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>46251</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>46253</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>46253</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>46253</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>46253</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>46253</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>46084</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>45238</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>45987</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>46097</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15503,7 +15503,7 @@
         <v>45174</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         <v>46097</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>46246</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>46253</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15800,7 +15800,7 @@
         <v>46105</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>46105</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>45504</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         <v>45860</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>45860</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>45861</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>45861</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>45861</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>45861</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>46114</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         <v>46260</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>45875</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>45867</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16799,7 +16799,7 @@
         <v>44893</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         <v>46133</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>45174</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>46133</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>46133</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>46133</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>44928</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>45161</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17398,7 +17398,7 @@
         <v>46310</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>46310</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17554,7 +17554,7 @@
         <v>46309</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>45168</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>46314</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>45516</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>45714</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>45989</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>45139</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         <v>45054</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>45154</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>45230</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>45167</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>46276</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>46276</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>46276</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>44893</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>46317</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18747,7 +18747,7 @@
         <v>46317</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>46317</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
         <v>45174</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>45154</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>45176</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>46154</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19210,7 +19210,7 @@
         <v>45719</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>45238</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44994</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19434,7 +19434,7 @@
         <v>44964</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19507,7 +19507,7 @@
         <v>45211</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19580,7 +19580,7 @@
         <v>45694</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>44792</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19726,7 +19726,7 @@
         <v>45643</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>45000</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
         <v>45201</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>45153</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>45153</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         <v>45178</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>45002</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>45639</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>45184</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>45625</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20466,7 +20466,7 @@
         <v>45162</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>45642</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>45646</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>45149</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>45203</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>45642</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>45201</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20987,7 +20987,7 @@
         <v>45022</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
         <v>45022</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>45160</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21211,7 +21211,7 @@
         <v>45193</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21284,7 +21284,7 @@
         <v>45190</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>45155</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>45174</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>45166</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21581,7 +21581,7 @@
         <v>44802</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>45022</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>44881</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21800,7 +21800,7 @@
         <v>45179</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21873,7 +21873,7 @@
         <v>45167</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21946,7 +21946,7 @@
         <v>45646</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>45148</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>45245</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22175,7 +22175,7 @@
         <v>45167</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         <v>45158</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>45156</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>45166</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22472,7 +22472,7 @@
         <v>45155</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22545,7 +22545,7 @@
         <v>45152</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22618,7 +22618,7 @@
         <v>45610</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>45750</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22764,7 +22764,7 @@
         <v>45645</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22842,7 +22842,7 @@
         <v>45167</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22920,7 +22920,7 @@
         <v>45170</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>45154</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>45166</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>45590</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23217,7 +23217,7 @@
         <v>45201</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23290,7 +23290,7 @@
         <v>45642</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>45162</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23436,7 +23436,7 @@
         <v>45187</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23514,7 +23514,7 @@
         <v>45189</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         <v>45152</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23660,7 +23660,7 @@
         <v>45159</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23733,7 +23733,7 @@
         <v>45601</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23811,7 +23811,7 @@
         <v>45170</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>45601</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>45645</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>45190</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>45153</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
         <v>45153</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>45193</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>45193</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>45180</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>45196</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24556,7 +24556,7 @@
         <v>45182</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>45646</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24707,7 +24707,7 @@
         <v>45204</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24780,7 +24780,7 @@
         <v>45193</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>45625</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24926,7 +24926,7 @@
         <v>45148</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>45195</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25072,7 +25072,7 @@
         <v>45153</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>45201</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25218,7 +25218,7 @@
         <v>45700</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>45516</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>45189</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>45232</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>45223</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>45167</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>45166</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>45166</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>45162</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>45225</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>45174</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>45149</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>45202</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>45229</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>45741</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>45267</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>45369</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>45694</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26557,7 +26557,7 @@
         <v>44575</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26630,7 +26630,7 @@
         <v>45180</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26703,7 +26703,7 @@
         <v>44967</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26776,7 +26776,7 @@
         <v>45167</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>45159</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>45520</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>45646</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>45229</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>44607</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
